--- a/artfynd/A 16185-2024 artfynd.xlsx
+++ b/artfynd/A 16185-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ3"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -782,54 +782,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>132414907</v>
+        <v>137279476</v>
       </c>
       <c r="B3" t="n">
-        <v>99195</v>
+        <v>83494</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Gropen, Gropen, Hjd</t>
+          <t>Gropen, Hjd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>471908</v>
+        <v>471898</v>
       </c>
       <c r="R3" t="n">
-        <v>6872418</v>
+        <v>6872488</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -856,12 +847,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -886,6 +877,117 @@
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137279476</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>132414907</v>
+      </c>
+      <c r="B4" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Gropen, Gropen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>471908</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6872418</v>
+      </c>
+      <c r="S4" t="n">
+        <v>20</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/132414907</t>
         </is>
@@ -895,6 +997,7 @@
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 16185-2024 artfynd.xlsx
+++ b/artfynd/A 16185-2024 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>137279476</v>
       </c>
       <c r="B3" t="n">
-        <v>83494</v>
+        <v>83504</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 16185-2024 artfynd.xlsx
+++ b/artfynd/A 16185-2024 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>137279476</v>
       </c>
       <c r="B3" t="n">
-        <v>83504</v>
+        <v>83507</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 16185-2024 artfynd.xlsx
+++ b/artfynd/A 16185-2024 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>137279476</v>
       </c>
       <c r="B3" t="n">
-        <v>83507</v>
+        <v>83512</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 16185-2024 artfynd.xlsx
+++ b/artfynd/A 16185-2024 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>137279476</v>
       </c>
       <c r="B3" t="n">
-        <v>83512</v>
+        <v>83523</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 16185-2024 artfynd.xlsx
+++ b/artfynd/A 16185-2024 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>137279476</v>
       </c>
       <c r="B3" t="n">
-        <v>83523</v>
+        <v>83524</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 16185-2024 artfynd.xlsx
+++ b/artfynd/A 16185-2024 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>137279476</v>
       </c>
       <c r="B3" t="n">
-        <v>83524</v>
+        <v>83526</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 16185-2024 artfynd.xlsx
+++ b/artfynd/A 16185-2024 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>137279476</v>
       </c>
       <c r="B3" t="n">
-        <v>83526</v>
+        <v>83530</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
